--- a/outputs_xlsx_solution/prog-loop.4-wide-NR-4.xlsx
+++ b/outputs_xlsx_solution/prog-loop.4-wide-NR-4.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>IS</t>
   </si>
   <si>
@@ -135,6 +138,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -627,7 +633,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -647,13 +653,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -676,10 +682,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -699,13 +705,13 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -725,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -740,7 +746,7 @@
         <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +766,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
         <v>14</v>
@@ -801,7 +807,7 @@
         <v>14</v>
       </c>
       <c r="O8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -821,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O9" t="s">
         <v>14</v>
       </c>
       <c r="P9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +844,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -847,25 +853,25 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -876,7 +882,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -885,16 +891,16 @@
         <v>9</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
         <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -905,7 +911,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -914,22 +920,22 @@
         <v>9</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P12" t="s">
         <v>14</v>
       </c>
       <c r="Q12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -952,7 +958,7 @@
         <v>14</v>
       </c>
       <c r="T13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -972,7 +978,7 @@
         <v>9</v>
       </c>
       <c r="S14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T14" t="s">
         <v>14</v>
@@ -987,7 +993,7 @@
         <v>14</v>
       </c>
       <c r="X14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1007,16 +1013,16 @@
         <v>9</v>
       </c>
       <c r="S15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T15" t="s">
         <v>14</v>
       </c>
       <c r="U15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -1036,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="S16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X16" t="s">
         <v>14</v>
@@ -1048,7 +1054,7 @@
         <v>14</v>
       </c>
       <c r="AA16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1068,13 +1074,13 @@
         <v>9</v>
       </c>
       <c r="T17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="s">
         <v>14</v>
       </c>
       <c r="AB17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -1085,7 +1091,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R18" t="s">
         <v>5</v>
@@ -1094,25 +1100,25 @@
         <v>9</v>
       </c>
       <c r="T18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X18" t="s">
         <v>14</v>
       </c>
       <c r="Y18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1123,7 +1129,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R19" t="s">
         <v>5</v>
@@ -1132,16 +1138,16 @@
         <v>9</v>
       </c>
       <c r="X19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="s">
         <v>14</v>
       </c>
       <c r="Z19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1152,7 +1158,7 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R20" t="s">
         <v>5</v>
@@ -1161,22 +1167,22 @@
         <v>9</v>
       </c>
       <c r="X20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB20" t="s">
         <v>14</v>
       </c>
       <c r="AC20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -1196,13 +1202,13 @@
         <v>9</v>
       </c>
       <c r="AA21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB21" t="s">
         <v>14</v>
       </c>
       <c r="AC21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1222,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="AB22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC22" t="s">
         <v>14</v>
@@ -1237,7 +1243,7 @@
         <v>14</v>
       </c>
       <c r="AG22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1257,16 +1263,16 @@
         <v>9</v>
       </c>
       <c r="AB23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC23" t="s">
         <v>14</v>
       </c>
       <c r="AD23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1286,10 +1292,10 @@
         <v>9</v>
       </c>
       <c r="AB24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="s">
         <v>14</v>
@@ -1301,7 +1307,7 @@
         <v>14</v>
       </c>
       <c r="AJ24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1321,13 +1327,13 @@
         <v>9</v>
       </c>
       <c r="AC25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ25" t="s">
         <v>14</v>
       </c>
       <c r="AK25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -1338,7 +1344,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T26" t="s">
         <v>5</v>
@@ -1347,25 +1353,25 @@
         <v>9</v>
       </c>
       <c r="AC26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG26" t="s">
         <v>14</v>
       </c>
       <c r="AH26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -1376,7 +1382,7 @@
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T27" t="s">
         <v>5</v>
@@ -1385,16 +1391,16 @@
         <v>9</v>
       </c>
       <c r="AG27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH27" t="s">
         <v>14</v>
       </c>
       <c r="AI27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -1405,7 +1411,7 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T28" t="s">
         <v>5</v>
@@ -1414,27 +1420,27 @@
         <v>9</v>
       </c>
       <c r="AG28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="s">
         <v>14</v>
       </c>
       <c r="AL28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -1442,7 +1448,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1450,15 +1456,15 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
@@ -1466,39 +1472,55 @@
         <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" t="s">
         <v>32</v>
       </c>
-      <c r="B38" t="s">
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
         <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
